--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Energia e impianti.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Energia e impianti.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <r>
       <t xml:space="preserve">
@@ -636,7 +636,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -701,9 +701,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -1480,7 +1477,7 @@
         <v>55</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D11" s="34" t="s">
         <v>55</v>
